--- a/InputData/elec/CRbQ/Cap Retirements before Quantization.xlsx
+++ b/InputData/elec/CRbQ/Cap Retirements before Quantization.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\elec\CRbQ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\Nevada\NV-eps\InputData\elec\CRbQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AD38C1-F330-456A-932F-C511B2D6FEAE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A169FB49-6316-4E4C-B9FC-C43095A46FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4050" yWindow="1515" windowWidth="24540" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8925" yWindow="555" windowWidth="18270" windowHeight="16470" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="14" r:id="rId1"/>
     <sheet name="CRbQ" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -337,7 +337,7 @@
       <alignment horizontal="left"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -345,8 +345,6 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="15">
     <cellStyle name="Body: normal cell" xfId="6" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -657,7 +655,7 @@
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -667,17 +665,17 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" t="s">
         <v>29</v>
       </c>
     </row>
@@ -685,17 +683,17 @@
       <c r="A9" s="2"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" t="s">
         <v>31</v>
       </c>
     </row>
@@ -879,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>528.85714285714289</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -975,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>100.83333333333331</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -987,16 +985,16 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>453.74999999999989</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>201.66666666666663</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>100.83333333333331</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -1791,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G11">
         <v>0</v>
